--- a/documentation/Tableau de synthèse.xlsx
+++ b/documentation/Tableau de synthèse.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iecm064.sharepoint.com/sites/int_SIO2SLAM/Documents partages/Encadrement PORTFOLIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\test portfolio\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="11_13326F3ED61FDE0C2D3468356C4017007C356263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F70606A-7890-4318-9110-2480D321B2E6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFE8DD-F803-489A-A120-487F8E77BFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$C$9:$C$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$C$9</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>▢ SISR</t>
-  </si>
-  <si>
-    <t>▢x SLAM</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -135,30 +132,16 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>NOM et prénom : RABIER Titouan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adresse URL du portfolio : </t>
   </si>
   <si>
     <t>Gestion des inventaires &amp; des incidents (OCS GLPI)</t>
   </si>
   <si>
-    <t>Création d'un site E-enseignement avec le CMS Wordpress</t>
+    <t xml:space="preserve">NOM et prénom : </t>
   </si>
   <si>
-    <t>Refonte du jeu Snake en C</t>
-  </si>
-  <si>
-    <t>Stage 2ème année
-Création de site wordpress pour une association d'évenementiel</t>
-  </si>
-  <si>
-    <t>Stage 1ère  année
-Création de site wordpress pour l'entreprise Appariteur</t>
-  </si>
-  <si>
-    <t>Création d'une agence web appelée LIAM's Group</t>
+    <t>▢ SLAM</t>
   </si>
 </sst>
 </file>
@@ -246,18 +229,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -663,7 +640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -726,93 +703,87 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -830,10 +801,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1137,56 +1104,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:47" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:47" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
-        <v>25</v>
+      <c r="A3" s="28" t="s">
+        <v>26</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="50" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="51"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="35"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:47" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="49"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
@@ -1194,67 +1161,67 @@
         <v>6</v>
       </c>
       <c r="H4" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48"/>
+    </row>
+    <row r="6" spans="1:47" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:47" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
-    </row>
-    <row r="6" spans="1:47" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="B6" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:47" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:47" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>20</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>21</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1291,22 +1258,22 @@
       <c r="AO7"/>
       <c r="AP7"/>
       <c r="AQ7"/>
-      <c r="AR7" s="29"/>
-      <c r="AS7" s="29"/>
-      <c r="AT7" s="29"/>
-      <c r="AU7" s="29"/>
+      <c r="AR7" s="26"/>
+      <c r="AS7" s="26"/>
+      <c r="AT7" s="26"/>
+      <c r="AU7" s="26"/>
     </row>
     <row r="8" spans="1:47" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
-        <v>22</v>
+      <c r="A8" s="38" t="s">
+        <v>21</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1342,21 +1309,21 @@
       <c r="AO8"/>
       <c r="AP8"/>
       <c r="AQ8"/>
-      <c r="AR8" s="29"/>
-      <c r="AS8" s="29"/>
-      <c r="AT8" s="29"/>
-      <c r="AU8" s="29"/>
+      <c r="AR8" s="26"/>
+      <c r="AS8" s="26"/>
+      <c r="AT8" s="26"/>
+      <c r="AU8" s="26"/>
     </row>
     <row r="9" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
       <c r="H9" s="15"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -1393,18 +1360,18 @@
       <c r="AO9"/>
       <c r="AP9"/>
       <c r="AQ9"/>
-      <c r="AR9" s="29"/>
-      <c r="AS9" s="29"/>
-      <c r="AT9" s="29"/>
-      <c r="AU9" s="29"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
     </row>
     <row r="10" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="8"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="14"/>
       <c r="H10" s="15"/>
       <c r="I10"/>
@@ -1442,22 +1409,20 @@
       <c r="AO10"/>
       <c r="AP10"/>
       <c r="AQ10"/>
-      <c r="AR10" s="29"/>
-      <c r="AS10" s="29"/>
-      <c r="AT10" s="29"/>
-      <c r="AU10" s="29"/>
+      <c r="AR10" s="26"/>
+      <c r="AS10" s="26"/>
+      <c r="AT10" s="26"/>
+      <c r="AU10" s="26"/>
     </row>
     <row r="11" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>28</v>
-      </c>
+      <c r="A11" s="21"/>
       <c r="B11" s="8"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="23"/>
+      <c r="F11" s="22"/>
       <c r="G11" s="14"/>
-      <c r="H11" s="26"/>
+      <c r="H11" s="23"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1493,10 +1458,10 @@
       <c r="AO11"/>
       <c r="AP11"/>
       <c r="AQ11"/>
-      <c r="AR11" s="29"/>
-      <c r="AS11" s="29"/>
-      <c r="AT11" s="29"/>
-      <c r="AU11" s="29"/>
+      <c r="AR11" s="26"/>
+      <c r="AS11" s="26"/>
+      <c r="AT11" s="26"/>
+      <c r="AU11" s="26"/>
     </row>
     <row r="12" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
@@ -1542,20 +1507,18 @@
       <c r="AO12"/>
       <c r="AP12"/>
       <c r="AQ12"/>
-      <c r="AR12" s="29"/>
-      <c r="AS12" s="29"/>
-      <c r="AT12" s="29"/>
-      <c r="AU12" s="29"/>
+      <c r="AR12" s="26"/>
+      <c r="AS12" s="26"/>
+      <c r="AT12" s="26"/>
+      <c r="AU12" s="26"/>
     </row>
     <row r="13" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="A13" s="21"/>
       <c r="B13" s="8"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="23"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="14"/>
       <c r="H13" s="15"/>
       <c r="I13"/>
@@ -1593,10 +1556,10 @@
       <c r="AO13"/>
       <c r="AP13"/>
       <c r="AQ13"/>
-      <c r="AR13" s="29"/>
-      <c r="AS13" s="29"/>
-      <c r="AT13" s="29"/>
-      <c r="AU13" s="29"/>
+      <c r="AR13" s="26"/>
+      <c r="AS13" s="26"/>
+      <c r="AT13" s="26"/>
+      <c r="AU13" s="26"/>
     </row>
     <row r="14" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
@@ -1642,22 +1605,20 @@
       <c r="AO14"/>
       <c r="AP14"/>
       <c r="AQ14"/>
-      <c r="AR14" s="29"/>
-      <c r="AS14" s="29"/>
-      <c r="AT14" s="29"/>
-      <c r="AU14" s="29"/>
+      <c r="AR14" s="26"/>
+      <c r="AS14" s="26"/>
+      <c r="AT14" s="26"/>
+      <c r="AU14" s="26"/>
     </row>
     <row r="15" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>32</v>
-      </c>
+      <c r="A15" s="21"/>
       <c r="B15" s="8"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
-      <c r="H15" s="25"/>
+      <c r="H15" s="23"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1693,10 +1654,10 @@
       <c r="AO15"/>
       <c r="AP15"/>
       <c r="AQ15"/>
-      <c r="AR15" s="29"/>
-      <c r="AS15" s="29"/>
-      <c r="AT15" s="29"/>
-      <c r="AU15" s="29"/>
+      <c r="AR15" s="26"/>
+      <c r="AS15" s="26"/>
+      <c r="AT15" s="26"/>
+      <c r="AU15" s="26"/>
     </row>
     <row r="16" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
@@ -1742,22 +1703,22 @@
       <c r="AO16"/>
       <c r="AP16"/>
       <c r="AQ16"/>
-      <c r="AR16" s="29"/>
-      <c r="AS16" s="29"/>
-      <c r="AT16" s="29"/>
-      <c r="AU16" s="29"/>
+      <c r="AR16" s="26"/>
+      <c r="AS16" s="26"/>
+      <c r="AT16" s="26"/>
+      <c r="AU16" s="26"/>
     </row>
     <row r="17" spans="1:47" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
-        <v>23</v>
+      <c r="A17" s="41" t="s">
+        <v>22</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1793,20 +1754,18 @@
       <c r="AO17"/>
       <c r="AP17"/>
       <c r="AQ17"/>
-      <c r="AR17" s="29"/>
-      <c r="AS17" s="29"/>
-      <c r="AT17" s="29"/>
-      <c r="AU17" s="29"/>
+      <c r="AR17" s="26"/>
+      <c r="AS17" s="26"/>
+      <c r="AT17" s="26"/>
+      <c r="AU17" s="26"/>
     </row>
     <row r="18" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>31</v>
-      </c>
+      <c r="A18" s="25"/>
       <c r="B18" s="8"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="14"/>
       <c r="H18" s="15"/>
       <c r="I18"/>
@@ -1844,13 +1803,13 @@
       <c r="AO18"/>
       <c r="AP18"/>
       <c r="AQ18"/>
-      <c r="AR18" s="29"/>
-      <c r="AS18" s="29"/>
-      <c r="AT18" s="29"/>
-      <c r="AU18" s="29"/>
+      <c r="AR18" s="26"/>
+      <c r="AS18" s="26"/>
+      <c r="AT18" s="26"/>
+      <c r="AU18" s="26"/>
     </row>
     <row r="19" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="8"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -1893,10 +1852,10 @@
       <c r="AO19"/>
       <c r="AP19"/>
       <c r="AQ19"/>
-      <c r="AR19" s="29"/>
-      <c r="AS19" s="29"/>
-      <c r="AT19" s="29"/>
-      <c r="AU19" s="29"/>
+      <c r="AR19" s="26"/>
+      <c r="AS19" s="26"/>
+      <c r="AT19" s="26"/>
+      <c r="AU19" s="26"/>
     </row>
     <row r="20" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
@@ -1942,10 +1901,10 @@
       <c r="AO20"/>
       <c r="AP20"/>
       <c r="AQ20"/>
-      <c r="AR20" s="29"/>
-      <c r="AS20" s="29"/>
-      <c r="AT20" s="29"/>
-      <c r="AU20" s="29">
+      <c r="AR20" s="26"/>
+      <c r="AS20" s="26"/>
+      <c r="AT20" s="26"/>
+      <c r="AU20" s="26">
         <f>+++++++AA9</f>
         <v>0</v>
       </c>
@@ -1994,10 +1953,10 @@
       <c r="AO21"/>
       <c r="AP21"/>
       <c r="AQ21"/>
-      <c r="AR21" s="29"/>
-      <c r="AS21" s="29"/>
-      <c r="AT21" s="29"/>
-      <c r="AU21" s="29"/>
+      <c r="AR21" s="26"/>
+      <c r="AS21" s="26"/>
+      <c r="AT21" s="26"/>
+      <c r="AU21" s="26"/>
     </row>
     <row r="22" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
@@ -2043,10 +2002,10 @@
       <c r="AO22"/>
       <c r="AP22"/>
       <c r="AQ22"/>
-      <c r="AR22" s="29"/>
-      <c r="AS22" s="29"/>
-      <c r="AT22" s="29"/>
-      <c r="AU22" s="29"/>
+      <c r="AR22" s="26"/>
+      <c r="AS22" s="26"/>
+      <c r="AT22" s="26"/>
+      <c r="AU22" s="26"/>
     </row>
     <row r="23" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
@@ -2092,10 +2051,10 @@
       <c r="AO23"/>
       <c r="AP23"/>
       <c r="AQ23"/>
-      <c r="AR23" s="29"/>
-      <c r="AS23" s="29"/>
-      <c r="AT23" s="29"/>
-      <c r="AU23" s="29"/>
+      <c r="AR23" s="26"/>
+      <c r="AS23" s="26"/>
+      <c r="AT23" s="26"/>
+      <c r="AU23" s="26"/>
     </row>
     <row r="24" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
@@ -2105,7 +2064,7 @@
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="29"/>
+      <c r="H24" s="26"/>
       <c r="I24" s="15"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2141,22 +2100,22 @@
       <c r="AO24"/>
       <c r="AP24"/>
       <c r="AQ24"/>
-      <c r="AR24" s="29"/>
-      <c r="AS24" s="29"/>
-      <c r="AT24" s="29"/>
-      <c r="AU24" s="29"/>
+      <c r="AR24" s="26"/>
+      <c r="AS24" s="26"/>
+      <c r="AT24" s="26"/>
+      <c r="AU24" s="26"/>
     </row>
     <row r="25" spans="1:47" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
-        <v>24</v>
+      <c r="A25" s="41" t="s">
+        <v>23</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2192,20 +2151,18 @@
       <c r="AO25"/>
       <c r="AP25"/>
       <c r="AQ25"/>
-      <c r="AR25" s="29"/>
-      <c r="AS25" s="29"/>
-      <c r="AT25" s="29"/>
-      <c r="AU25" s="29"/>
+      <c r="AR25" s="26"/>
+      <c r="AS25" s="26"/>
+      <c r="AT25" s="26"/>
+      <c r="AU25" s="26"/>
     </row>
     <row r="26" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>30</v>
-      </c>
+      <c r="A26" s="25"/>
       <c r="B26" s="8"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="15"/>
       <c r="I26"/>
@@ -2243,13 +2200,13 @@
       <c r="AO26"/>
       <c r="AP26"/>
       <c r="AQ26"/>
-      <c r="AR26" s="29"/>
-      <c r="AS26" s="29"/>
-      <c r="AT26" s="29"/>
-      <c r="AU26" s="29"/>
+      <c r="AR26" s="26"/>
+      <c r="AS26" s="26"/>
+      <c r="AT26" s="26"/>
+      <c r="AU26" s="26"/>
     </row>
     <row r="27" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="8"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -2292,10 +2249,10 @@
       <c r="AO27"/>
       <c r="AP27"/>
       <c r="AQ27"/>
-      <c r="AR27" s="29"/>
-      <c r="AS27" s="29"/>
-      <c r="AT27" s="29"/>
-      <c r="AU27" s="29"/>
+      <c r="AR27" s="26"/>
+      <c r="AS27" s="26"/>
+      <c r="AT27" s="26"/>
+      <c r="AU27" s="26"/>
     </row>
     <row r="28" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
@@ -2341,10 +2298,10 @@
       <c r="AO28"/>
       <c r="AP28"/>
       <c r="AQ28"/>
-      <c r="AR28" s="29"/>
-      <c r="AS28" s="29"/>
-      <c r="AT28" s="29"/>
-      <c r="AU28" s="29"/>
+      <c r="AR28" s="26"/>
+      <c r="AS28" s="26"/>
+      <c r="AT28" s="26"/>
+      <c r="AU28" s="26"/>
     </row>
     <row r="29" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
@@ -2390,10 +2347,10 @@
       <c r="AO29"/>
       <c r="AP29"/>
       <c r="AQ29"/>
-      <c r="AR29" s="29"/>
-      <c r="AS29" s="29"/>
-      <c r="AT29" s="29"/>
-      <c r="AU29" s="29"/>
+      <c r="AR29" s="26"/>
+      <c r="AS29" s="26"/>
+      <c r="AT29" s="26"/>
+      <c r="AU29" s="26"/>
     </row>
     <row r="30" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
@@ -2439,10 +2396,10 @@
       <c r="AO30"/>
       <c r="AP30"/>
       <c r="AQ30"/>
-      <c r="AR30" s="29"/>
-      <c r="AS30" s="29"/>
-      <c r="AT30" s="29"/>
-      <c r="AU30" s="29"/>
+      <c r="AR30" s="26"/>
+      <c r="AS30" s="26"/>
+      <c r="AT30" s="26"/>
+      <c r="AU30" s="26"/>
     </row>
     <row r="31" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
@@ -2488,10 +2445,10 @@
       <c r="AO31"/>
       <c r="AP31"/>
       <c r="AQ31"/>
-      <c r="AR31" s="29"/>
-      <c r="AS31" s="29"/>
-      <c r="AT31" s="29"/>
-      <c r="AU31" s="29"/>
+      <c r="AR31" s="26"/>
+      <c r="AS31" s="26"/>
+      <c r="AT31" s="26"/>
+      <c r="AU31" s="26"/>
     </row>
     <row r="32" spans="1:47" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
@@ -2537,10 +2494,10 @@
       <c r="AO32"/>
       <c r="AP32"/>
       <c r="AQ32"/>
-      <c r="AR32" s="29"/>
-      <c r="AS32" s="29"/>
-      <c r="AT32" s="29"/>
-      <c r="AU32" s="29"/>
+      <c r="AR32" s="26"/>
+      <c r="AS32" s="26"/>
+      <c r="AT32" s="26"/>
+      <c r="AU32" s="26"/>
     </row>
     <row r="33" spans="1:47" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
@@ -2586,10 +2543,10 @@
       <c r="AO33"/>
       <c r="AP33"/>
       <c r="AQ33"/>
-      <c r="AR33" s="29"/>
-      <c r="AS33" s="29"/>
-      <c r="AT33" s="29"/>
-      <c r="AU33" s="29"/>
+      <c r="AR33" s="26"/>
+      <c r="AS33" s="26"/>
+      <c r="AT33" s="26"/>
+      <c r="AU33" s="26"/>
     </row>
     <row r="34" spans="1:47" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:47" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2639,11 +2596,6 @@
     <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2651,16 +2603,41 @@
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F136CB4AE69C04489071CEF15422A7D7" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="c4b4fdb095601ea6d2cbe93ad6a6b1db">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="191d0fcf-6d89-4c90-807a-10f37b8d7a4c" xmlns:ns3="9a7dc87b-2be1-4fee-871a-355a79ca984c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="151f77297e777b87b35019f3692944ad" ns2:_="" ns3:_="">
     <xsd:import namespace="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
@@ -2855,27 +2832,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A3CCF3B-7B88-440F-8A0A-FBED7FBF06E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
+    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{240DE218-FED0-48EE-B696-C7623217CB73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07FE53A1-2C1A-4D2C-A9F9-4A4248857B5D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2892,29 +2874,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{240DE218-FED0-48EE-B696-C7623217CB73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A3CCF3B-7B88-440F-8A0A-FBED7FBF06E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
-    <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/Tableau de synthèse.xlsx
+++ b/documentation/Tableau de synthèse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\test portfolio\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FFE8DD-F803-489A-A120-487F8E77BFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B523C4-F949-4439-812B-BFFBACECAF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
